--- a/artfynd/A 23706-2023 artfynd.xlsx
+++ b/artfynd/A 23706-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23706-2023 artfynd.xlsx
+++ b/artfynd/A 23706-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109987197</v>
+        <v>109987185</v>
       </c>
       <c r="B2" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +706,11 @@
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410696.1885309097</v>
+        <v>410587</v>
       </c>
       <c r="R2" t="n">
-        <v>7045662.404449715</v>
+        <v>7045275</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +751,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109987194</v>
+        <v>109987186</v>
       </c>
       <c r="B3" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410521.9925323506</v>
+        <v>410690</v>
       </c>
       <c r="R3" t="n">
-        <v>7045619.532177522</v>
+        <v>7045648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,24 +852,14 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>ringhack äldre</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109987193</v>
+        <v>109987191</v>
       </c>
       <c r="B4" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410538.6764304347</v>
+        <v>410519</v>
       </c>
       <c r="R4" t="n">
-        <v>7045481.565027236</v>
+        <v>7045455</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,24 +958,14 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ringhack färska</t>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109987207</v>
+        <v>109987193</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,34 +1003,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Älgtjärnen Kall, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410542.5568778676</v>
+        <v>410539</v>
       </c>
       <c r="R5" t="n">
-        <v>7045428.776548903</v>
+        <v>7045482</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1064,14 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ringhack färska</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,15 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109987201</v>
+        <v>109987194</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,34 +1109,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Älgtjärnen Kall, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410609.1467095221</v>
+        <v>410522</v>
       </c>
       <c r="R6" t="n">
-        <v>7045141.618204114</v>
+        <v>7045619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,19 +1170,14 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,15 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109987199</v>
+        <v>109987195</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,34 +1215,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Älgtjärnen Kall, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410576.5379128131</v>
+        <v>410654</v>
       </c>
       <c r="R7" t="n">
-        <v>7045413.088986745</v>
+        <v>7045651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,19 +1276,14 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,15 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109987195</v>
+        <v>109987196</v>
       </c>
       <c r="B8" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410653.4059872589</v>
+        <v>410716</v>
       </c>
       <c r="R8" t="n">
-        <v>7045651.106041392</v>
+        <v>7045658</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,19 +1382,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1495,15 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109987196</v>
+        <v>109987197</v>
       </c>
       <c r="B9" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410716.6218498009</v>
+        <v>410696</v>
       </c>
       <c r="R9" t="n">
-        <v>7045657.813411163</v>
+        <v>7045663</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,19 +1488,9 @@
           <t>2023-06-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1613,248 +1519,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>109987191</v>
-      </c>
-      <c r="B10" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Älgtjärnen Kall, Jmt</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>410519.1634296213</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7045455.32761074</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>109987186</v>
-      </c>
-      <c r="B11" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Älgtjärnen Kall, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>410689.5097581228</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7045647.414079836</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-06-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>ringhack</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23706-2023 artfynd.xlsx
+++ b/artfynd/A 23706-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987185</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987186</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987191</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987193</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,6 +1226,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987194</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987195</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1413,6 +1448,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987196</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,8 +1559,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109987197</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>